--- a/research/reports/ec2_benchmark_complete_results.xlsx
+++ b/research/reports/ec2_benchmark_complete_results.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latency &amp; Throughput" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Class Performance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confusion Matrix" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed Inferences" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Latency &amp; Throughput" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Per-Class Performance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Confusion Matrix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Detailed Inferences" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>UNESCO Project Deliverable | Generated: 2026-09-02 14:51:54 UTC | Target: http://localhost:8001</t>
+          <t>UNESCO Project Deliverable | Generated: 2026-09-02 15:18:55 UTC | Target: http://127.0.0.1:8001</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>26.67%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2063.155 ms</t>
+          <t>1.574 ms</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>2088.638 ms</t>
+          <t>1.712 ms</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>0.327 ms</t>
+          <t>1.574 ms</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>0.48 requests/sec</t>
+          <t>617.13 requests/sec</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>0.0% Pass</t>
+          <t>100.0% Pass</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>2063.155</v>
+        <v>1.574</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>0.327</v>
+        <v>1.574</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>2065.135</v>
+        <v>1.561</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>2080.968</v>
+        <v>1.664</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2088.638</v>
+        <v>1.712</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>0.467</v>
+        <v>1.712</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>2098.72</v>
+        <v>1.822</v>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>2035.761</v>
+        <v>1.464</v>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>2101.241</v>
+        <v>1.983</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>17.968</v>
+        <v>0.081</v>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
@@ -1016,16 +1016,16 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" s="9" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>0</v>
@@ -1057,7 +1057,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
@@ -1080,29 +1080,29 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0.5714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1112,29 +1112,29 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" s="9" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>0</v>
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>0</v>
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1334,14 +1334,14 @@
         <v>0</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1401,7 +1401,7 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="23" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:23.871</t>
+          <t>2026-09-02 15:18:55.246</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1510,20 +1510,20 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>R2L</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>86.59</v>
+        <v>0</v>
       </c>
       <c r="F4" s="8" t="n">
-        <v>2083.237</v>
+        <v>1.983</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>0.274</v>
+        <v>1.983</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.003001548971654122</v>
+        <v>0.003589817272521849</v>
       </c>
       <c r="P4" s="4" t="n">
         <v>1</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:25.953</t>
+          <t>2026-09-02 15:18:55.248</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1576,20 +1576,20 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Probe</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>49.52</v>
+        <v>0</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>2041.342</v>
+        <v>1.74</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.286</v>
+        <v>1.74</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="N5" s="4" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.003946531788320605</v>
+        <v>0.0166526884192604</v>
       </c>
       <c r="P5" s="4" t="n">
         <v>0.98</v>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:27.994</t>
+          <t>2026-09-02 15:18:55.250</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1642,20 +1642,20 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>99.98</v>
+        <v>0</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>2046.991</v>
+        <v>1.82</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0.312</v>
+        <v>1.82</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -1686,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.9283204670640894</v>
+        <v>0.9489752761786928</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.04922520625596894</v>
+        <v>0.1077556893922516</v>
       </c>
     </row>
     <row r="7">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:30.043</t>
+          <t>2026-09-02 15:18:55.252</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1708,20 +1708,20 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>R2L</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>56.6</v>
+        <v>0</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>2035.761</v>
+        <v>1.648</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>0.267</v>
+        <v>1.648</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
@@ -1752,10 +1752,10 @@
         <v>1032</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.8041935977109597</v>
+        <v>0.8444712288201272</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.9859912979053297</v>
+        <v>0.9662201666398594</v>
       </c>
     </row>
     <row r="8">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:32.077</t>
+          <t>2026-09-02 15:18:55.254</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1774,29 +1774,29 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Probe</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>2052.378</v>
+        <v>1.615</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>0.344</v>
+        <v>1.615</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+        <v>500</v>
+      </c>
+      <c r="I8" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:34.131</t>
+          <t>2026-09-02 15:18:55.255</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1840,29 +1840,29 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>R2L</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
-        <v>53.01</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>2035.861</v>
+        <v>1.712</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>0.323</v>
+        <v>1.712</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+        <v>500</v>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:36.165</t>
+          <t>2026-09-02 15:18:55.257</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1906,20 +1906,20 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>R2L</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>74.64</v>
+        <v>0</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>2101.241</v>
+        <v>1.606</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>0.242</v>
+        <v>1.606</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:38.268</t>
+          <t>2026-09-02 15:18:55.259</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1972,20 +1972,20 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>R2L</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E11" s="8" t="n">
-        <v>86.54000000000001</v>
+        <v>0</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>2071.084</v>
+        <v>1.671</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>0.289</v>
+        <v>1.671</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="N11" s="4" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.001363239386584654</v>
+        <v>0.001132609637350255</v>
       </c>
       <c r="P11" s="4" t="n">
         <v>1</v>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:40.338</t>
+          <t>2026-09-02 15:18:55.260</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -2038,20 +2038,20 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Probe</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2057.91</v>
+        <v>1.534</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>0.317</v>
+        <v>1.534</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="N12" s="4" t="n">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.01929076107248087</v>
+        <v>0.01756279300121558</v>
       </c>
       <c r="P12" s="4" t="n">
         <v>0.98</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:42.396</t>
+          <t>2026-09-02 15:18:55.262</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2104,20 +2104,20 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E13" s="8" t="n">
-        <v>99.95</v>
+        <v>0</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>2077.564</v>
+        <v>1.559</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>0.272</v>
+        <v>1.559</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -2148,10 +2148,10 @@
         <v>0</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.8660135501674535</v>
+        <v>0.9881605536936449</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.05109611011837007</v>
+        <v>0.06003488394711742</v>
       </c>
     </row>
     <row r="14">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:44.474</t>
+          <t>2026-09-02 15:18:55.264</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2170,20 +2170,20 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Probe</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>51.04</v>
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2065.538</v>
+        <v>1.723</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>0.633</v>
+        <v>1.723</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -2214,10 +2214,10 @@
         <v>1032</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8552544772053151</v>
+        <v>0.8623741793340824</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.9388763187109956</v>
+        <v>0.9681516995546361</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:46.541</t>
+          <t>2026-09-02 15:18:55.265</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -2236,29 +2236,29 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Probe</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>2065.135</v>
+        <v>1.521</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0.378</v>
+        <v>1.521</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+        <v>500</v>
+      </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K15" s="9" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:48.604</t>
+          <t>2026-09-02 15:18:55.267</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -2302,29 +2302,29 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>R2L</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>53.01</v>
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>2077.071</v>
+        <v>1.621</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0.396</v>
+        <v>1.621</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+        <v>500</v>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:50.682</t>
+          <t>2026-09-02 15:18:55.269</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -2368,20 +2368,20 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>R2L</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
-        <v>74.64</v>
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>2061.403</v>
+        <v>1.482</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>0.283</v>
+        <v>1.482</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 14:51:52.743</t>
+          <t>2026-09-02 15:18:55.270</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2434,20 +2434,20 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>R2L</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>86.68000000000001</v>
+        <v>0</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>2074.816</v>
+        <v>1.549</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>0.292</v>
+        <v>1.549</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>FAIL (&gt;=100ms)</t>
+          <t>PASS (&lt;100ms)</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -2475,13 +2475,5623 @@
         </is>
       </c>
       <c r="N18" s="4" t="n">
-        <v>313</v>
+        <v>285</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.006065795472084093</v>
+        <v>0.008588357105920368</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.272</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>1.633</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0.0106423349457768</v>
+      </c>
+      <c r="P19" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.273</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M20" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>0.9186775056927956</v>
+      </c>
+      <c r="P20" s="4" t="n">
+        <v>0.1114935066332119</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.275</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O21" s="4" t="n">
+        <v>0.8196369042253137</v>
+      </c>
+      <c r="P21" s="4" t="n">
+        <v>0.9207179333505201</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.277</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>1.482</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>1.482</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.278</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I23" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.280</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I24" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M24" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.281</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="n">
+        <v>194</v>
+      </c>
+      <c r="O25" s="4" t="n">
+        <v>0.00268939731024916</v>
+      </c>
+      <c r="P25" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.283</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="O26" s="4" t="n">
+        <v>0.007686976923865358</v>
+      </c>
+      <c r="P26" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.284</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>1.479</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>1.479</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4" t="n">
+        <v>0.9699994127405421</v>
+      </c>
+      <c r="P27" s="4" t="n">
+        <v>0.07021526759372924</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.286</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O28" s="4" t="n">
+        <v>0.8969175587642834</v>
+      </c>
+      <c r="P28" s="4" t="n">
+        <v>0.9879826543546709</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.288</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>1.659</v>
+      </c>
+      <c r="G29" s="8" t="n">
+        <v>1.659</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.289</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>1.498</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>1.498</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O30" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.291</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>1.599</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>1.599</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.292</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="O32" s="4" t="n">
+        <v>0.01493121482295953</v>
+      </c>
+      <c r="P32" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.294</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="n">
+        <v>199</v>
+      </c>
+      <c r="O33" s="4" t="n">
+        <v>0.001540640683384806</v>
+      </c>
+      <c r="P33" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.296</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>1.694</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="4" t="n">
+        <v>0.9324893795078441</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>0.1072378312423677</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.297</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>1.487</v>
+      </c>
+      <c r="G35" s="8" t="n">
+        <v>1.487</v>
+      </c>
+      <c r="H35" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O35" s="4" t="n">
+        <v>0.8569462202080336</v>
+      </c>
+      <c r="P35" s="4" t="n">
+        <v>0.9230345216745329</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.299</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.301</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>1.482</v>
+      </c>
+      <c r="G37" s="8" t="n">
+        <v>1.482</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.302</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.304</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>1.691</v>
+      </c>
+      <c r="G39" s="8" t="n">
+        <v>1.691</v>
+      </c>
+      <c r="H39" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="n">
+        <v>314</v>
+      </c>
+      <c r="O39" s="4" t="n">
+        <v>0.01253708267852501</v>
+      </c>
+      <c r="P39" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.305</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="O40" s="4" t="n">
+        <v>0.005371394274315258</v>
+      </c>
+      <c r="P40" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.307</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="G41" s="8" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M41" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="4" t="n">
+        <v>0.8553750690590312</v>
+      </c>
+      <c r="P41" s="4" t="n">
+        <v>0.05005934428903098</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.309</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="H42" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M42" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O42" s="4" t="n">
+        <v>0.8944378712622771</v>
+      </c>
+      <c r="P42" s="4" t="n">
+        <v>0.9457692122340173</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.310</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="G43" s="8" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.312</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.313</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>1.487</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>1.487</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I45" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.315</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M46" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>254</v>
+      </c>
+      <c r="O46" s="4" t="n">
+        <v>0.002824710187354438</v>
+      </c>
+      <c r="P46" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.316</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>1.464</v>
+      </c>
+      <c r="H47" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>0.01717158706259448</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.318</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="4" t="n">
+        <v>0.9066942668194189</v>
+      </c>
+      <c r="P48" s="4" t="n">
+        <v>0.0628051808337176</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.320</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="G49" s="8" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O49" s="4" t="n">
+        <v>0.844121988518917</v>
+      </c>
+      <c r="P49" s="4" t="n">
+        <v>0.9682991586777003</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.321</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>1.498</v>
+      </c>
+      <c r="G50" s="8" t="n">
+        <v>1.498</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.323</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>1.596</v>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>1.596</v>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N51" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O51" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.324</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="G52" s="8" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M52" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.326</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G53" s="8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>257</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0.007002691687605516</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.328</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="G54" s="8" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M54" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>0.002955555937807901</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.329</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="G55" s="8" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="4" t="n">
+        <v>0.8553774441193305</v>
+      </c>
+      <c r="P55" s="4" t="n">
+        <v>0.1011639915597925</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.331</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M56" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O56" s="4" t="n">
+        <v>0.8047754338968414</v>
+      </c>
+      <c r="P56" s="4" t="n">
+        <v>0.9377089584330405</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.332</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="G57" s="8" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M57" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.334</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>1.529</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M58" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O58" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.336</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>1.684</v>
+      </c>
+      <c r="G59" s="8" t="n">
+        <v>1.684</v>
+      </c>
+      <c r="H59" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O59" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.337</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="G60" s="8" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="O60" s="4" t="n">
+        <v>0.0162859593077857</v>
+      </c>
+      <c r="P60" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.339</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>1.604</v>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>1.604</v>
+      </c>
+      <c r="H61" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N61" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="O61" s="4" t="n">
+        <v>0.008193810056197072</v>
+      </c>
+      <c r="P61" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.340</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G62" s="8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>0.9114152740724714</v>
+      </c>
+      <c r="P62" s="4" t="n">
+        <v>0.08194905885507839</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.342</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>1.562</v>
+      </c>
+      <c r="G63" s="8" t="n">
+        <v>1.562</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M63" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O63" s="4" t="n">
+        <v>0.7784984610578447</v>
+      </c>
+      <c r="P63" s="4" t="n">
+        <v>0.9263229654070484</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.344</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>1.637</v>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>1.637</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M64" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.345</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>1.479</v>
+      </c>
+      <c r="G65" s="8" t="n">
+        <v>1.479</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O65" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.347</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="8" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="G66" s="8" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.349</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="8" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="G67" s="8" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="H67" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="n">
+        <v>299</v>
+      </c>
+      <c r="O67" s="4" t="n">
+        <v>0.008935033035111135</v>
+      </c>
+      <c r="P67" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.350</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="8" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="G68" s="8" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="O68" s="4" t="n">
+        <v>0.01095473088591137</v>
+      </c>
+      <c r="P68" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.352</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>1.657</v>
+      </c>
+      <c r="G69" s="8" t="n">
+        <v>1.657</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="4" t="n">
+        <v>0.8675142544188561</v>
+      </c>
+      <c r="P69" s="4" t="n">
+        <v>0.09996265262733291</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.353</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="G70" s="8" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O70" s="4" t="n">
+        <v>0.7626030420266494</v>
+      </c>
+      <c r="P70" s="4" t="n">
+        <v>0.9300752903124463</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.355</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>1.598</v>
+      </c>
+      <c r="G71" s="8" t="n">
+        <v>1.598</v>
+      </c>
+      <c r="H71" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.357</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G72" s="8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M72" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.358</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="G73" s="8" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.360</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>1.637</v>
+      </c>
+      <c r="G74" s="8" t="n">
+        <v>1.637</v>
+      </c>
+      <c r="H74" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L74" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M74" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="O74" s="4" t="n">
+        <v>0.01133599061776904</v>
+      </c>
+      <c r="P74" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.361</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="G75" s="8" t="n">
+        <v>1.499</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M75" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="O75" s="4" t="n">
+        <v>0.01458984735179946</v>
+      </c>
+      <c r="P75" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.363</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>1.626</v>
+      </c>
+      <c r="G76" s="8" t="n">
+        <v>1.626</v>
+      </c>
+      <c r="H76" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M76" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="4" t="n">
+        <v>0.9236202550427672</v>
+      </c>
+      <c r="P76" s="4" t="n">
+        <v>0.04643579829168035</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.365</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="G77" s="8" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="H77" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O77" s="4" t="n">
+        <v>0.805022204550656</v>
+      </c>
+      <c r="P77" s="4" t="n">
+        <v>0.9868726820170591</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.366</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="G78" s="8" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="H78" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M78" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.368</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="G79" s="8" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="H79" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K79" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M79" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N79" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O79" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.369</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="G80" s="8" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="H80" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K80" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L80" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M80" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N80" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.371</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="G81" s="8" t="n">
+        <v>1.629</v>
+      </c>
+      <c r="H81" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K81" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M81" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N81" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="O81" s="4" t="n">
+        <v>0.01742640647234366</v>
+      </c>
+      <c r="P81" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.373</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="G82" s="8" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="H82" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M82" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N82" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="O82" s="4" t="n">
+        <v>0.01326592189290792</v>
+      </c>
+      <c r="P82" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.374</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="G83" s="8" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="H83" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K83" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M83" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="4" t="n">
+        <v>0.913122211813445</v>
+      </c>
+      <c r="P83" s="4" t="n">
+        <v>0.04925617652659516</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.376</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="G84" s="8" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="H84" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M84" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N84" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O84" s="4" t="n">
+        <v>0.8911082455074014</v>
+      </c>
+      <c r="P84" s="4" t="n">
+        <v>0.933072068766325</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.378</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>1.487</v>
+      </c>
+      <c r="G85" s="8" t="n">
+        <v>1.487</v>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L85" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M85" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.379</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="G86" s="8" t="n">
+        <v>1.614</v>
+      </c>
+      <c r="H86" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K86" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M86" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N86" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.381</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="8" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="G87" s="8" t="n">
+        <v>1.547</v>
+      </c>
+      <c r="H87" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M87" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N87" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.382</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="8" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="G88" s="8" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="H88" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K88" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L88" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M88" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N88" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="O88" s="4" t="n">
+        <v>0.005721821885283567</v>
+      </c>
+      <c r="P88" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.384</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="8" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="G89" s="8" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="H89" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L89" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M89" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N89" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="O89" s="4" t="n">
+        <v>0.01230477762020748</v>
+      </c>
+      <c r="P89" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.386</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="8" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="G90" s="8" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K90" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L90" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M90" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="4" t="n">
+        <v>0.9281049228937839</v>
+      </c>
+      <c r="P90" s="4" t="n">
+        <v>0.1127321522057226</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.387</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="8" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="G91" s="8" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="H91" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M91" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N91" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O91" s="4" t="n">
+        <v>0.7532083342810483</v>
+      </c>
+      <c r="P91" s="4" t="n">
+        <v>0.957095284125708</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.389</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="G92" s="8" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="H92" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K92" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M92" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.390</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="G93" s="8" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="H93" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M93" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N93" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.392</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="G94" s="8" t="n">
+        <v>1.663</v>
+      </c>
+      <c r="H94" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K94" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L94" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M94" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N94" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.394</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G95" s="8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M95" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="O95" s="4" t="n">
+        <v>0.01193150380008957</v>
+      </c>
+      <c r="P95" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.395</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>1.587</v>
+      </c>
+      <c r="G96" s="8" t="n">
+        <v>1.587</v>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K96" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M96" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N96" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="O96" s="4" t="n">
+        <v>0.01665140298117299</v>
+      </c>
+      <c r="P96" s="4" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.397</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="8" t="n">
+        <v>1.563</v>
+      </c>
+      <c r="G97" s="8" t="n">
+        <v>1.563</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L97" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M97" s="9" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="N97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="4" t="n">
+        <v>0.8799963480207049</v>
+      </c>
+      <c r="P97" s="4" t="n">
+        <v>0.05596320367362476</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.398</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>DoS</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="8" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="G98" s="8" t="n">
+        <v>1.566</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I98" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="inlineStr">
+        <is>
+          <t>icmp</t>
+        </is>
+      </c>
+      <c r="L98" s="9" t="inlineStr">
+        <is>
+          <t>eco_i</t>
+        </is>
+      </c>
+      <c r="M98" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N98" s="4" t="n">
+        <v>1032</v>
+      </c>
+      <c r="O98" s="4" t="n">
+        <v>0.8445403390797276</v>
+      </c>
+      <c r="P98" s="4" t="n">
+        <v>0.9437382764914304</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.400</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Probe</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G99" s="8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I99" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L99" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M99" s="9" t="inlineStr">
+        <is>
+          <t>REJ</t>
+        </is>
+      </c>
+      <c r="N99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="4" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.402</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>R2L</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="8" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="G100" s="8" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I100" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L100" s="9" t="inlineStr">
+        <is>
+          <t>ftp</t>
+        </is>
+      </c>
+      <c r="M100" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N100" s="4" t="n">
+        <v>280</v>
+      </c>
+      <c r="O100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.403</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>U2R</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="8" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="G101" s="8" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K101" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L101" s="9" t="inlineStr">
+        <is>
+          <t>telnet</t>
+        </is>
+      </c>
+      <c r="M101" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="n">
+        <v>2400</v>
+      </c>
+      <c r="O101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.405</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G102" s="8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I102" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="inlineStr">
+        <is>
+          <t>tcp</t>
+        </is>
+      </c>
+      <c r="L102" s="9" t="inlineStr">
+        <is>
+          <t>http</t>
+        </is>
+      </c>
+      <c r="M102" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="O102" s="4" t="n">
+        <v>0.001585046777825634</v>
+      </c>
+      <c r="P102" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02 15:18:55.407</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="8" t="n">
+        <v>1.544</v>
+      </c>
+      <c r="G103" s="8" t="n">
+        <v>1.544</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I103" s="11" t="inlineStr">
+        <is>
+          <t>MISCLASSIFIED</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>PASS (&lt;100ms)</t>
+        </is>
+      </c>
+      <c r="K103" s="9" t="inlineStr">
+        <is>
+          <t>udp</t>
+        </is>
+      </c>
+      <c r="L103" s="9" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
+      <c r="M103" s="9" t="inlineStr">
+        <is>
+          <t>SF</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="O103" s="4" t="n">
+        <v>0.008352113709899496</v>
+      </c>
+      <c r="P103" s="4" t="n">
+        <v>0.98</v>
       </c>
     </row>
   </sheetData>
